--- a/Memory_Verses.xlsx
+++ b/Memory_Verses.xlsx
@@ -431,9 +431,140 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A2:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Genesis 1:1 </t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Genesis 17:1 </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Exodus 15:26 </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Exodus 34:6 </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Exodus </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Leviticus 11:44 </t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Numbers 23:19 </t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Deuteronomy 7:9 </t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Deuteronomy 32:4 </t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1 Samuel 2:2 </t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2 Samuel 22:31 </t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1 Kings 8:27 </t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2 Chronicles 7:14 </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Memory_Verses.xlsx
+++ b/Memory_Verses.xlsx
@@ -431,136 +431,201 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:B14"/>
+  <dimension ref="A2:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"> Genesis 1:1 </t>
         </is>
       </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"In the beginning God created the heavens and the earth." </t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"> Genesis 17:1 </t>
         </is>
       </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">God; walk before Me and be blameless.'" </t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"> Exodus 15:26 </t>
         </is>
       </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brought on the Egyptians. For I am the Lord who heals you.'" </t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"> Exodus 34:6 </t>
         </is>
       </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">longsuffering, and abounding in goodness and truth, </t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"> Exodus </t>
         </is>
       </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourth generation. </t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"> Leviticus 11:44 </t>
         </is>
       </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">holy. Neither shall you defile yourselves with any creeping thing that creeps on the earth. </t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"> Numbers 23:19 </t>
         </is>
       </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">not do? Or has He spoken, and will He not make it good?" </t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"> Deuteronomy 7:9 </t>
         </is>
       </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a thousand generations with those who love Him and keep His commandments;" </t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"> Deuteronomy 32:4 </t>
         </is>
       </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Righteous and upright is He." </t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"> 1 Samuel 2:2 </t>
         </is>
       </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"No one is holy like the Lord, For there is none besides You, Nor is there any rock like our God." </t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"> 2 Samuel 22:31 </t>
         </is>
       </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"As for God, His way is perfect; The word of the Lord is proven; He is a shield to all who trust in Him." </t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"> 1 Kings 8:27 </t>
         </is>
       </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How much less this temple which I have built!" </t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"> 2 Chronicles 7:14 </t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">their wicked ways, then I will hear from heaven, and I will forgive their sin and will heal their land. </t>
         </is>
       </c>
     </row>

--- a/Memory_Verses.xlsx
+++ b/Memory_Verses.xlsx
@@ -460,7 +460,7 @@
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">God; walk before Me and be blameless.'" </t>
+          <t xml:space="preserve">"When Abram was ninety-nine years old, the Lord appeared to Abram and said to him, 'I am Almighty God; walk before Me and be blameless.'" </t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">brought on the Egyptians. For I am the Lord who heals you.'" </t>
+          <t xml:space="preserve">"and said, 'If you diligently heed the voice of the Lord your God and do what is right in His sight, give ear to His commandments and keep all His statutes, I will put none of the diseases on you which I have brought on the Egyptians. For I am the Lord who heals you.'" </t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">longsuffering, and abounding in goodness and truth, </t>
+          <t xml:space="preserve">"And the Lord passed before him and proclaimed, 'The Lord, the Lord God, merciful and gracious, longsuffering, and abounding in goodness and truth, </t>
         </is>
       </c>
     </row>
@@ -505,7 +505,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">fourth generation. </t>
+          <t xml:space="preserve">34:7Keeping mercy for thousands, forgiving iniquity and transgression and sin, by no means clearing the guilty, visiting the iniquity of the fathers upon the children and the children’s children to the third and the fourth generation. </t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">holy. Neither shall you defile yourselves with any creeping thing that creeps on the earth. </t>
+          <t xml:space="preserve">For I am the LORD your God. You shall therefore consecrate yourselves, and you shall be holy; for I am holy. Neither shall you defile yourselves with any creeping thing that creeps on the earth. </t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">not do? Or has He spoken, and will He not make it good?" </t>
+          <t xml:space="preserve">God is not a man, that He should lie, Nor a son of man, that He should repent. Has He said, and will He not do? Or has He spoken, and will He not make it good?" </t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">a thousand generations with those who love Him and keep His commandments;" </t>
+          <t xml:space="preserve">"Therefore know that the Lord your God, He is God, the faithful God who keeps covenant and mercy for a thousand generations with those who love Him and keep His commandments;" </t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Righteous and upright is He." </t>
+          <t xml:space="preserve">"He is the Rock, His work is perfect; For all His ways are justice, A God of truth and without injustice; Righteous and upright is He." </t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">How much less this temple which I have built!" </t>
+          <t xml:space="preserve">"But will God indeed dwell on the earth? Behold, heaven and the heaven of heavens cannot contain You. How much less this temple which I have built!" </t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">their wicked ways, then I will hear from heaven, and I will forgive their sin and will heal their land. </t>
+          <t xml:space="preserve">their wicked ways, then I will hear from heaven, and I will forgive their sin and will heal their land. My people who are called by My name humble themselves, and pray and seek My face, and turn from their wicked ways, then I will hear from heaven, and I will forgive their sin and will heal their land. </t>
         </is>
       </c>
     </row>

--- a/Memory_Verses.xlsx
+++ b/Memory_Verses.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:C14"/>
+  <dimension ref="A2:C301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -625,7 +625,4307 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">their wicked ways, then I will hear from heaven, and I will forgive their sin and will heal their land. My people who are called by My name humble themselves, and pray and seek My face, and turn from their wicked ways, then I will hear from heaven, and I will forgive their sin and will heal their land. </t>
+          <t xml:space="preserve">My people who are called by My name humble themselves, and pray and seek My face, and turn from their wicked ways, then I will hear from heaven, and I will forgive their sin and will heal their land. </t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Job 37:23 </t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"As for the Almighty, we cannot find Him; He is excellent in power, In judgment and abundant justice; He does not oppress." </t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 1:1 </t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blessed is the man Who walks not in the counsel of the ungodly, Nor stands in the path of sinners, Nor sits in the seat of the scornful; </t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 1:2 </t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">But his delight is in the law of the Lord, And in His law he meditates day and night. </t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 1:3 </t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He shall be like a tree Planted by the rivers of water, That brings forth its fruit in its season, Whose leaf also shall not wither; And whatever he does shall prosper. </t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 3:3 </t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"But You, O Lord, are a shield for me, my glory and the One who lifts up my head." </t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 4:8 </t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"I will both lie down in peace, and sleep; for You alone, O Lord, make me dwell in safety." </t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 5:12 </t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"For You, O Lord, will bless the righteous; with favor You will surround him as with a shield." </t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 6:2 </t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Have mercy on me, O Lord, for I am weak; O Lord, heal me, for my bones are troubled." </t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 8:3 </t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">When I consider Your heavens, the work of Your fingers, The moon and the stars, which You have ordained, </t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 8:4 </t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What is man that You are mindful of him, And the son of man that You visit him? </t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 8:5 </t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">For You have made him a little lower than the angels, And You have crowned him with glory and honor. </t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 15:1 </t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Lord, who may abide in Your tabernacle? Who may dwell in Your holy hill? </t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 15:2 </t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He who walks uprightly, and works righteousness, and speaks the truth in his heart;" </t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 16:11 </t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"You will show me the path of life; in Your presence is fullness of joy; at Your right hand are pleasures forevermore." </t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 18:2 </t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The Lord is my rock and my fortress and my deliverer; my God, my strength, in whom I will trust; my shield and the horn of my salvation, my stronghold." </t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 18:30 </t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"As for God, His way is perfect; the word of the Lord is proven; He is a shield to all who trust in Him." </t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 19:14 </t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Let the words of my mouth and the meditation of my heart be acceptable in Your sight, O Lord, my strength and my Redeemer." </t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 20:7 </t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Some trust in chariots, and some in horses; but we will remember the name of the Lord our God." </t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 23:1 </t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The Lord is my shepherd; I shall not want. </t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 23:2 </t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He makes me to lie down in green pastures; He leads me beside the still waters. </t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 23:3 </t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">. He restores my soul; He leads me in the paths of righteousness for His name’s sake. </t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 23:4 </t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">. Yea, though I walk through the valley of the shadow of death, I will fear no evil; for You are with me; Your rod and Your staff, they comfort me. </t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 23:5 </t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You prepare a table before me in the presence of my enemies; You anoint my head with oil; my cup runs over. </t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 23:6 </t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">. Surely goodness and mercy shall follow me all the days of my life; and I will dwell in the house of the Lord forever." </t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 24:8 </t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Who is this King of glory? The Lord strong and mighty, the Lord mighty in battle." </t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 25:4 </t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Show me Your ways, O Lord; teach me Your paths. </t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 25:5 </t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lead me in Your truth and teach me, for You are the God of my salvation; on You I wait all the day." </t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 25:8 </t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Good and upright is the Lord; therefore He teaches sinners in the way." </t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 27:1 </t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The Lord is my light and my salvation; whom shall I fear? The Lord is the strength of my life; of whom shall I be afraid?" </t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 27:14 </t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Wait on the Lord; be of good courage, and He shall strengthen your heart; wait, I say, on the Lord!" </t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 30:2 </t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lord my God, I cried out to You, and You healed me. </t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 30:5 </t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"For His anger is but for a moment, His favor is for a life; weeping may endure for a night, but joy comes in the morning." </t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 31:24 </t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Be of good courage, and He shall strengthen your heart, all you who hope in the Lord." </t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 32:8 </t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"I will instruct you and teach you in the way you should go; I will guide you with My eye." </t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 33:12 </t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Blessed is the nation whose God is the Lord, the people He has chosen as His own inheritance." </t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 34:8 </t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Oh, taste and see that the Lord is good; blessed is the man who trusts in Him!" </t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 34:19 </t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Many are the afflictions of the righteous, but the Lord delivers him out of them all." </t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 36:5 </t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Your mercy, O Lord, is in the heavens; Your faithfulness reaches to the clouds." </t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 37:4 </t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Delight yourself also in the Lord, and He shall give you the desires of your heart. </t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 37:5 </t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">“Commit your way to the Lord, trust also in Him, and He shall bring it to pass." </t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 37:23 </t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The steps of a good man are ordered by the Lord, and He delights in his way." </t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 40:1 </t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"I waited patiently for the Lord; and He inclined to me, and heard my cry." </t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 41:3 </t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The Lord will strengthen him on his bed of illness; You will maintain him on his sickbed." </t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 46:1 </t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"God is our refuge and strength, a very present help in trouble." </t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 47:7 </t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"For God is the King of all the earth; sing praises with understanding." </t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 48:14 </t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"For this is God, our God forever and ever; He will be our guide even to death." </t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 51:10 </t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Create in me a clean heart, O God, and renew a steadfast spirit within me." </t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 51:10 </t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Cast your burden on the Lord, and He shall sustain you; He shall never permit the righteous to be moved." </t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 56:3 </t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Whenever I am afraid, I will trust in You." </t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 61:2 </t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"From the end of the earth I will cry to You, when my heart is overwhelmed; lead me to the rock that is higher than I." </t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 62:11 </t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"God has spoken once, twice I have heard this: That power belongs to God." </t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 66:18 </t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"If I regard iniquity in my heart, the Lord will not hear." </t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 68:20 </t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Our God is the God of salvation; and to God the Lord belong escapes from death." </t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 71:5 </t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"For You are my hope, O Lord God; You are my trust from my youth." </t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 73:26 </t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"My flesh and my heart fail; but God is the strength of my heart and my portion forever." </t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 84:11 </t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"For the Lord God is a sun and shield; the Lord will give grace and glory; no good thing will He withhold from those who walk uprightly." </t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 86:11 </t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Teach me Your way, O Lord; I will walk in Your truth; unite my heart to fear Your name." </t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 86:15 </t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"But You, O Lord, are a God full of compassion, and gracious, longsuffering and abundant in mercy and truth." </t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 90:2 </t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Before the mountains were brought forth, or ever You had formed the earth and the world, even from everlasting to everlasting, You are God." </t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 91:1 </t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"He who dwells in the secret place of the Most High shall abide under the shadow of the Almighty. </t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 91:2 </t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I will say of the Lord, 'He is my refuge and my fortress; my God, in Him I will trust.'" </t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 99:9 </t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Exalt the Lord our God, and worship at His holy hill; for the Lord our God is holy." </t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 100:4 </t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Enter into His gates with thanksgiving, and into His courts with praise. Be thankful to Him, and bless His name." </t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 103:1 </t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Bless the Lord, O my soul; and all that is within me, bless His holy name! </t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 103:2 </t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bless the Lord, O my soul, and forget not all His benefits: </t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 103:3 </t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Who forgives all your iniquities, who heals all your diseases, </t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 103:4 </t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">who redeems your life from destruction, who crowns you with lovingkindness and tender mercies, </t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 103.5 </t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">who satisfies your mouth with good things, so that your youth is renewed like the eagle’s." </t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 103:8 </t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The Lord is merciful and gracious, slow to anger, and abounding in mercy." </t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 107:20 </t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"He sent His word and healed them, and delivered them from their destructions." </t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 111:9 </t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"He has sent redemption to His people; He has commanded His covenant forever: Holy and awesome is His name." </t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 112:1 </t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Praise the Lord! Blessed is the man who fears the Lord, who delights greatly in His commandments." </t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 115:3 </t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"But our God is in heaven; He does whatever He pleases." </t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 116:1 </t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"I love the Lord, because He has heard my voice and my supplications. </t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 116:2 </t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Because He has inclined His ear to me, therefore I will call upon Him as long as I live." </t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 118:24 </t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"This is the day the Lord has made; we will rejoice and be glad in it." </t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 119:9 </t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"How can a young man cleanse his way? By taking heed according to Your word." </t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 119:11 </t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Your word I have hidden in my heart, that I might not sin against You." </t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 119:105 </t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Your word is a lamp to my feet and a light to my path." </t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 121:1 </t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"I will lift up my eyes to the hills—from whence comes my help? </t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 121:2 </t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">My help comes from the Lord, who made heaven and earth." </t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 130:5 </t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"I wait for the Lord, my soul waits, and in His word I do hope." </t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 138:8 </t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The Lord will perfect that which concerns me; Your mercy, O Lord, endures forever; do not forsake the works of Your hands." </t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 139:7 </t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Where can I go from Your Spirit? Or where can I flee from Your presence? </t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 139:8 </t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">. If I ascend into heaven, You are there; if I make my bed in hell, behold, You are there. </t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 139:9 </t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If I take the wings of the morning, and dwell in the uttermost parts of the sea, even there Your hand shall lead me, and Your right hand shall hold me." </t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 143:8 </t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Cause me to hear Your lovingkindness in the morning, for in You do I trust; cause me to know the way in which I should walk, for I lift up my soul to You." </t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 145:17 </t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The Lord is righteous in all His ways, gracious in all His works." </t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 145:18 </t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The Lord is near to all who call upon Him, to all who call upon Him in truth." </t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 147:3 </t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"He heals the brokenhearted and binds up their wounds." </t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 147:5 </t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Great is our Lord, and mighty in power; His understanding is infinite." </t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Psalm 150:6 </t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Let everything that has breath praise the Lord. Praise the Lord!" </t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 1:5 </t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"A wise man will hear and increase learning, And a man of understanding will attain wise counsel," </t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 1:7 </t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The fear of the Lord is the beginning of knowledge, But fools despise wisdom and instruction." </t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 2:6 </t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"For the Lord gives wisdom; From His mouth come knowledge and understanding;" </t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 3:5-6 </t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Trust in the Lord with all your heart, And lean not on your own understanding; In all your ways acknowledge Him, And He shall direct your paths." </t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 3:7 </t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Do not be wise in your own eyes; Fear the Lord and depart from evil." </t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 3:11 </t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"My son, do not despise the chastening of the Lord, Nor be weary of His correction; </t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 3:12 </t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">For whom the Lord loves He corrects, Just as a father the son in whom he delights." </t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 3:19 </t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The Lord by wisdom founded the earth; By understanding He established the heavens;" </t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 4:7 </t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Wisdom is the principal thing; Therefore get wisdom. And in all your getting, get understanding." </t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 4:23 </t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Keep your heart with all diligence, For out of it spring the issues of life." </t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 6:6 </t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Go to the ant, you sluggard! Consider her ways and be wise </t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 8:13 </t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The fear of the Lord is to hate evil; Pride and arrogance and the evil way and the perverse mouth I hate." </t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 9:10 </t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The fear of the Lord is the beginning of wisdom, And the knowledge of the Holy One is understanding." </t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 10:9 </t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"He who walks with integrity walks securely, But he who perverts his ways will become known." </t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 10:12 </t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Hatred stirs up strife, But love covers all sins." </t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 10:17 </t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"He who keeps instruction is in the way of life, But he who refuses correction goes astray." </t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 11:2 </t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"When pride comes, then comes shame; But with the humble is wisdom." </t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 11:25 </t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The generous soul will be made rich, And he who waters will also be watered himself." </t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 11:30 </t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The fruit of the righteous is a tree of life, And he who wins souls is wise." </t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 12:1 </t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Whoever loves instruction loves knowledge, But he who hates correction is stupid." </t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 12:18 </t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"There is one who speaks like the piercings of a sword, But the tongue of the wise promotes health." </t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 12:25 </t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Anxiety in the heart of man causes depression, But a good word makes it glad." </t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 13:3 </t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"He who guards his mouth preserves his life, But he who opens wide his lips shall have destruction." </t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 13:10 </t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"By pride comes nothing but strife, But with the well-advised is wisdom." </t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 14:12 </t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"There is a way that seems right to a man, But its end is the way of death." </t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 15:1 </t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"A soft answer turns away wrath, But a harsh word stirs up anger." </t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 15:13 </t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"A merry heart makes a cheerful countenance, But by sorrow of the heart the spirit is broken." </t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 16:3 </t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Commit your works to the Lord, And your thoughts will be established." </t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 16:9 </t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"A man’s heart plans his way, But the Lord directs his steps." </t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 16:18 </t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Pride goes before destruction, And a haughty spirit before a fall." </t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 17:22 </t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"A merry heart does good, like medicine, But a broken spirit dries the bones." </t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 18:10 </t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The name of the Lord is a strong tower; The righteous run to it and are safe." </t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 18:21 </t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Death and life are in the power of the tongue, And those who love it will eat its fruit." </t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 20:1 </t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(Proverbs) "Wine is a mocker, Strong drink is a brawler, And whoever is led astray by it is not wise." </t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 20:22 </t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Do not say, 'I will recompense evil'; Wait for the Lord, and He will save you." </t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 21:3 </t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"To do righteousness and justice Is more acceptable to the Lord than sacrifice." </t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 21:21 </t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"He who follows righteousness and mercy Finds life, righteousness, and honor." </t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 22:1 </t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"A good name is to be chosen rather than great riches, Loving favor rather than silver and gold." </t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 22:6 </t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Train up a child in the way he should go, And when he is old he will not depart from it." </t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 23:4 </t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Do not overwork to be rich; Because of your own understanding, cease! </t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 23:5 </t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Will you set your eyes on that which is not? For riches certainly make themselves wings; They fly away like an eagle toward heaven." </t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 24:3 </t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Through wisdom a house is built, And by understanding it is established; </t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 24:4 </t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">By knowledge the rooms are filled With all precious and pleasant riches." </t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 24:16 </t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"For a righteous man may fall seven times And rise again, But the wicked shall fall by calamity." </t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 25:11 </t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"A word fitly spoken is like apples of gold in settings of silver." </t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 27:17 </t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"As iron sharpens iron, So a man sharpens the countenance of his friend." </t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 28:13 </t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"He who covers his sins will not prosper, But whoever confesses and forsakes them will have mercy." </t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proverbs 30:5 </t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Every word of God is pure; He is a shield to those who put their trust in Him." </t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Isaiah 6:3 </t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"And one cried to another and said: 'Holy, holy, holy is the Lord of hosts; The whole earth is full of His glory!'" </t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Isaiah 38:16 </t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"O Lord, by these things men live; And in all these things is the life of my spirit; So You will restore me and make me live." </t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Isaiah 40:28 </t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Have you not known? Have you not heard? The everlasting God, the Lord, The Creator of the ends of the earth, Neither faints nor is weary. His understanding is unsearchable." </t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Isaiah 40:29 </t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He gives power to the weak, And to those who have no might He increases strength. </t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Isaiah 40:30 </t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Even the youths shall faint and be weary, And the young men shall utterly fall,. </t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Isaiah 41:10 </t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Fear not, for I am with you; Be not dismayed, for I am your God. I will strengthen you, Yes, I will help you, I will uphold you with My righteous right hand." </t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Isaiah 53:5 </t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"But He was wounded for our transgressions, He was bruised for our iniquities; The chastisement for our peace was upon Him, And by His stripes we are healed." </t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Isaiah 57:15 </t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"For thus says the High and Lofty One Who inhabits eternity, whose name is Holy: 'I dwell in the high and holy place, With him who has a contrite and humble spirit” </t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Jeremiah 10:10 </t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"But the Lord is the true God; He is the living God and the everlasting King..." </t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Jeremiah 30:17 </t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"'For I will restore health to you And heal you of your wounds,' says the Lord..." </t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Jeremiah 33:6 </t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Behold, I will bring it health and healing; I will heal them and reveal to them the abundance of peace and truth." </t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Lamentations 3:22 </t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Through the Lord’s mercies we are not consumed, Because His compassions fail not. </t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Lamentations 3:23 </t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">They are new every morning; Great is Your faithfulness. </t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Hosea 6:1 </t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Come, and let us return to the Lord; For He has torn, but He will heal us; He has stricken, but He will bind us up." </t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Malachi 3:6 </t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"For I am the Lord, I do not change; Therefore you are not consumed, O sons of Jacob." </t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 4:23 </t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"And Jesus went about all Galilee, teaching in their synagogues, preaching the gospel of the kingdom, and healing all kinds of sickness and all kinds of disease among the people." </t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 5:3 </t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Blessed are the poor in spirit, for theirs is the kingdom of heaven </t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 5:4 </t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blessed are those who mourn, For they shall be comforted </t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 5:5 </t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blessed are the meek, For they shall inherit the earth. </t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 5:6 </t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blessed are those who are persecuted for righteousness’ sake, for theirs is the kingdom of heaven. </t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 5:14 </t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are the light of the world. A city that is set on a hill cannot be hidden. </t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 5:44 </t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"But I say to you, love your enemies, bless those who curse you, do good to those who hate you and pray for those who spitefully use you and persecute you. </t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 6:9 </t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In this manner, therefore, pray "Our Father in heaven, Hallowed be Your name. </t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 6:10 </t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Your kingdom come. Your will be done On earth as it is in heaven." </t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 6:11 </t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Give us this day our daily bread. </t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 6:12 </t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">And forgive us our debts, As we forgive our debtors. </t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 6:33 </t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"But seek first the kingdom of God and His righteousness, and all these things shall be added to you." </t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 7:7 </t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Ask, and it will be given to you; seek, and you will find; knock, and it will be opened to you" </t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 7:12 </t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Therefore, whatever you want men to do to you, do also to them, for this is the Law and the Prophets." </t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 10:39 </t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"He who finds his life will lose it, and he who loses his life for My sake will find it." </t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 11:28 </t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Come to Me, all you who labor and are heavy laden, and I will give you rest." </t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 12:15 </t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">But when Jesus knew it, He withdrew from there. And great multitudes followed Him, and He healed them all. </t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 13:44 </t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Again, the kingdom of heaven is like treasure hidden in a field, which a man found and hid; and for joy over it he goes and sells all that he has and buys that field." </t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 14:14 </t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"And when Jesus went out He saw a great multitude; and He was moved with compassion for them, and healed their sick." </t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 15:30 </t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Then great multitudes came to Him, having with them the lame, blind, mute, maimed, and many others; and they laid them down at Jesus’ feet, and He healed them." </t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 16:24 </t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Then Jesus said to His disciples, 'If anyone desires to come after Me, let him deny himself, and take up his cross, and follow Me.'" </t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 17:18 </t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"And Jesus rebuked the demon, and it came out of him; and the child was cured from that very hour." </t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 18:3 </t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"...Assuredly, I say to you, unless you are converted and become as little children, you will by no means enter the kingdom of heaven." </t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 18:20 </t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"For where two or three are gathered together in My name, I am there in the midst of them." </t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 19:14 </t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"But Jesus said, 'Let the little children come to Me, and do not forbid them; for of such is the kingdom of heaven.'" </t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 22:37 </t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Jesus said to him, '“You shall love the Lord your God with all your heart, with all your soul, and with all your mind.” </t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 22:38 </t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This is the first and great commandment. </t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 22:39 </t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">And the second is like it: “You shall love your neighbor as yourself.” </t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 23:12 </t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"And whoever exalts himself will be humbled, and he who humbles himself will be exalted." </t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 24:35 </t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Heaven and earth will pass away, but My words will by no means pass away." </t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 25:40 </t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">And the King will answer and say to them, ‘Assuredly, I say to you, inasmuch as you did it to one of the least of these My brethren, you did it to Me.’ </t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 26:41 </t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Watch and pray, lest you enter into temptation. The spirit indeed is willing, but the flesh is weak." </t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Matthew 28:19 </t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go therefore and make disciples of all the nations, baptizing them in the name of the Father and of the Son and of the Holy Spirit. </t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Mark 1:34 </t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Then He healed many who were sick with various diseases, and cast out many demons; and He did not allow the demons to speak, because they knew Him. </t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Mark 3:10 </t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"For He healed many, so that as many as had afflictions pressed about Him to touch Him." </t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Mark 5:34 </t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"And He said to her, 'Daughter, your faith has made you well. Go in peace, and be healed of your affliction.'" </t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Mark 7:37 </t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">And they were astonished beyond measure, saying, “He has done all things well. He makes both the deaf to hear and the mute to speak.” </t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Mark 9:35 </t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">And He sat down, called the twelve, and said to them, “If anyone desires to be first, he shall be last of all and servant of all.” </t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Mark 10:52 </t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Then Jesus said to him, 'Go your way; your faith has made you well.' And immediately he received his sight and followed Jesus on the road." </t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Mark 11:24 </t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Therefore I say to you, whatever things you ask when you pray, believe that you receive them, and you will have them." </t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Mark 16:15 </t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"And He said to them, 'Go into all the world and preach the gospel to every creature.'" </t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Luke 4:18 </t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"'The Spirit of the Lord is upon Me, Because He has anointed Me To preach the gospel to the poor; He has sent Me to heal the brokenhearted...'" </t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Luke 6:19 </t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"And the whole multitude sought to touch Him, for power went out from Him and healed them all." </t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Luke 6:27 </t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"But I say to you who hear: Love your enemies, do good to those who hate you," </t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Luke 6:31 </t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"And just as you want men to do to you, you also do to them likewise." </t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Luke 7:21 </t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"And that very hour He cured many of infirmities, afflictions, and evil spirits; and to many blind He gave sight." </t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Luke 8:48 </t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"And He said to her, 'Daughter, be of good cheer; your faith has made you well. Go in peace.'" </t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Luke 9:23 </t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Then He said to them all, 'If anyone desires to come after Me, let him deny himself, and take up his cross daily, and follow Me.'" </t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Luke 10:27 </t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"So he answered and said, '“You shall love the Lord your God with all your heart, with all your soul, with all your strength, and with all your mind,” and “your neighbor as yourself.” </t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Luke 11:9 </t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"So I say to you, ask, and it will be given to you; seek, and you will find; knock, and it will be opened to you." </t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Luke 12:15 </t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"And He said to them, 'Take heed and beware of covetousness, for one’s life does not consist in the abundance of the things he possesses.'" </t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Luke 13:12 </t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"But when Jesus saw her, He called her to Him and said to her, 'Woman, you are loosed from your infirmity.'" </t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Luke 14:27 </t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"And whoever does not bear his cross and come after Me cannot be My disciple." </t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Luke 15:7 </t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"I say to you that likewise there will be more joy in heaven over one sinner who repents than over ninety-nine just persons who need no repentance." </t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Luke 17:14 </t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"So when He saw them, He said to them, 'Go, show yourselves to the priests.' And so it was that as they went, they were cleansed." </t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Luke 17:33 </t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Whoever seeks to save his life will lose it, and whoever loses his life will preserve it." </t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Luke 18:1 </t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Then He spoke a parable to them, that men always ought to pray and not lose heart," </t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Luke 19:10 </t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"for the Son of Man has come to seek and to save that which was lost." </t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Luke 21:36 </t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Watch therefore, and pray always that you may be counted worthy to escape all these things that will come to pass, and to stand before the Son of Man." </t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> John 1:12 </t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"But as many as received Him, to them He gave the right to become children of God, to those who believe in His name:" </t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> John 3:3 </t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Jesus answered and said to him, 'Most assuredly, I say to you, unless one is born again, he cannot see the kingdom of God.'" </t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> John 3:16 </t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"For God so loved the world that He gave His only begotten Son, that whoever believes in Him should not perish but have everlasting life." </t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> John 4:24 </t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"God is Spirit, and those who worship Him must worship in spirit and truth." </t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> John 5:8 </t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Jesus said to him, 'Rise, take up your bed and walk.' </t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> John 5:9 </t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">And immediately the man was made well, took up his bed, and walked." </t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> John 6:35 </t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"And Jesus said to them, 'I am the bread of life. He who comes to Me shall never hunger, and he who believes in Me shall never thirst.'" </t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> John 6:47 </t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Most assuredly, I say to you, he who believes in Me has everlasting life." </t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> John 8:12 </t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Then Jesus spoke to them again, saying, 'I am the light of the world. He who follows Me shall not walk in darkness, but have the light of life.'" </t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> John 8:36 </t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Therefore if the Son makes you free, you shall be free indeed." </t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> John 10:10 </t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The thief does not come except to steal, and to kill, and to destroy. I have come that they may have life, and that they may have it more abundantly." </t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> John 10:28 </t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"And I give them eternal life, and they shall never perish; neither shall anyone snatch them out of My hand." </t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> John 11:25 </t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Jesus said to her, 'I am the resurrection and the life. He who believes in Me, though he may die, he shall live.'" </t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> John 12:26 </t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"If anyone serves Me, let him follow Me; and where I am, there My servant will be also. If anyone serves Me, him My Father will honor." </t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> John 13:34 </t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"A new commandment I give to you, that you love one another; as I have loved you, that you also love one another." </t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> John 14:1 </t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Let not your heart be troubled; you believe in God, believe also in Me." </t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> John 14:6 </t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Jesus said to him, 'I am the way, the truth, and the life. No one comes to the Father except through Me.'" </t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> John 14:27 </t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Peace I leave with you, My peace I give to you; not as the world gives do I give to you. Let not your heart be troubled, neither let it be afraid." </t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> John 15:5 </t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"I am the vine, you are the branches. He who abides in Me, and I in him, bears much fruit; for without Me you can do nothing." </t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> John 15:12 </t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"This is My commandment, that you love one another as I have loved you." </t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> John 16:33 </t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"These things I have spoken to you, that in Me you may have peace. In the world you will have tribulation; but be of good cheer, I have overcome the world." </t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> John 17:3 </t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"And this is eternal life, that they may know You, the only true God, and Jesus Christ whom You have sent." </t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> John 17:17 </t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Sanctify them by Your truth. Your word is truth." </t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> John 20:31 </t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"But these are written that you may believe that Jesus is the Christ, the Son of God, and that believing you may have life in His name." </t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Acts 2:38 </t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Then Peter said to them, 'Repent, and let every one of you be baptized in the name of Jesus Christ for the remission of sins; and you shall receive the gift of the Holy Spirit.'" </t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Acts 3:6 </t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Then Peter said, 'Silver and gold I do not have, but what I do have I give you: In the name of Jesus Christ of Nazareth, rise up and walk.'" </t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Acts 4:12 </t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Nor is there salvation in any other, for there is no other name under heaven given among men by which we must be saved." </t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Acts 9:34 </t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"And Peter said to him, 'Aeneas, Jesus Christ heals you. Arise and make your bed.' Then he arose immediately." </t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Acts 10:38 </t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"How God anointed Jesus of Nazareth with the Holy Spirit and with power, who went about doing good and healing all who were oppressed by the devil, for God was with Him." </t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Acts 16:31 </t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"So they said, 'Believe on the Lord Jesus Christ, and you will be saved, you and your household.'" </t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Romans 1:16 </t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"For I am not ashamed of the gospel of Christ, for it is the power of God to salvation for everyone who believes, for the Jew first and also for the Greek." </t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Romans 3:23 </t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"For all have sinned and fall short of the glory of God, </t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Romans 4:5 </t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"But to him who does not work but believes on Him who justifies the ungodly, his faith is accounted for righteousness," </t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Romans 5:1 </t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Therefore, having been justified by faith, we have peace with God through our Lord Jesus Christ," </t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Romans 5:8 </t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"But God demonstrates His own love toward us, in that while we were still sinners, Christ died for us." </t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Romans 6:23 </t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"For the wages of sin is death, but the gift of God is eternal life in Christ Jesus our Lord." </t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Romans 8:1 </t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"There is therefore now no condemnation to those who are in Christ Jesus, who do not walk according to the flesh, but according to the Spirit." </t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Romans 8:16 </t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The Spirit Himself bears witness with our spirit that we are the children of God," </t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Romans 8:38 </t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"For I am persuaded that neither death nor life, nor angels nor principalities nor powers, nor things present nor things to come, </t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Romans 8:39 </t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nor height nor depth, nor any other created thing, shall be able to separate us from the love of God which is in Christ Jesus our Lord. </t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Romans 9:16 </t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"So then it is not of him who wills, nor of him who runs, but of God who shows mercy." </t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Romans 11:6 </t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"And if by grace, then it is no longer of works; otherwise grace is no longer grace." </t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Romans 11:33 </t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Oh, the depth of the riches both of the wisdom and knowledge of God! How unsearchable are His judgments and His ways past finding out!" </t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1 Corinthians 1:9 </t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"God is faithful, by whom you were called into the fellowship of His Son, Jesus Christ our Lord." </t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2 Corinthians 5:17 </t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Therefore, if anyone is in Christ, he is a new creation; old things have passed away; behold, all things have become new." </t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2 Corinthians 5:21 </t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"For He made Him who knew no sin to be sin for us, that we might become the righteousness of God in Him." </t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Galatians 3:26 </t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"For you are all sons of God through faith in Christ Jesus." </t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Ephesians 1:7 </t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"In Him we have redemption through His blood, the forgiveness of sins, according to the riches of His grace" </t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Ephesians 2:8 </t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"For by grace you have been saved through faith, and that not of yourselves; it is the gift of God." </t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1 Timothy 2:5 </t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"For there is one God and one Mediator between God and men, the Man Christ Jesus," </t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2 Timothy 2:13 </t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"If we are faithless, He remains faithful; He cannot deny Himself." </t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Titus 1:2 </t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"In hope of eternal life which God, who cannot lie, promised before time began," </t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Titus 2:11 </t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"For the grace of God that brings salvation has appeared to all men," </t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Hebrews 7:25 </t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Therefore He is also able to save to the uttermost those who come to God through Him, since He always lives to make intercession for them." </t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Hebrews 9:28 </t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"So Christ was offered once to bear the sins of many. To those who eagerly wait for Him He will appear a second time, apart from sin, for salvation." </t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Hebrews 10:10 </t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"By that will we have been sanctified through the offering of the body of Jesus Christ once for all." </t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Hebrews 11:1 </t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Now faith is the substance of things hoped for, the evidence of things not seen. </t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Hebrews 11:6 </t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"But without faith it is impossible to please Him, for he who comes to God must believe that He is, and that He is a rewarder of those who diligently seek Him." </t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Hebrews 12:2 </t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Looking unto Jesus, the author and finisher of our faith who for the joy that was set before Him endured the cross, despising the shame, and has sat down at the right hand of the throne of God. </t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Hebrews 13:8 </t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Jesus Christ is the same yesterday, today, and forever." </t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> James 5:14 </t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">: Is anyone among you sick? Let him call for the elders of the church, and let them pray over him, anointing him with oil in the name of the Lord. </t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> James 5:15 </t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">and the prayer of faith will save the sick, and the Lord will raise him up." </t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1 Peter 2:9 </t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">But you are a chosen generation, a royal priesthood, a holy nation, His own special people, that you may proclaim the praises of Him who called you out of darkness into His marvelous light. </t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1 Peter 2:24 </t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Who Himself bore our sins in His own body on the tree, that we, having died to sins, might live for righteousness—by whose stripes you were healed. </t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>292</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1 John 1:5 </t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"This is the message which we have heard from Him and declare to you, that God is light and in Him is no darkness at all." </t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1 John 1:9 </t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"If we confess our sins, He is faithful and just to forgive us our sins and to cleanse us from all unrighteousness." </t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1 John 4:8 </t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"He who does not love does not know God, for God is love." </t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1 John 4:9 </t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"In this the love of God was manifested toward us, that God has sent His only begotten Son into the world, that we might live through Him." </t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1 John 5:11 </t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"And this is the testimony: that God has given us eternal life, and this life is in His Son. </t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1 John 5:12 </t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He who has the Son has life; he who does not have the Son of God does not have life." </t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Jude 1:24 </t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Now to Him who is able to keep you from stumbling, and to present you faultless before the presence of His glory with exceeding joy," </t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Revelation 3:20 </t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Behold, I stand at the door and knock. If anyone hears My voice and opens the door, I will come in to him and dine with him, and he with Me." </t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Revelation 21:4 </t>
         </is>
       </c>
     </row>
